--- a/歌词翻译/livedance_歌词对照_插白补充.xlsx
+++ b/歌词翻译/livedance_歌词对照_插白补充.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="10500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="歌词对照" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="声部变体" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="插白补充" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歌词对照" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声部变体" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插白补充" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>来和我们一起跳吧！</t>
+          <t>Enako炭，来和我们一起跳吧！</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>同上。『Enako』为CoZ听写的呼喊，游戏文本查无此人；用户拍板去名。</t>
+          <t>同上。『Enako』为CoZ听写的呼喊（游戏文本查无此名，但音频确有喊名字）；用户拍板保留，-chan 按本补丁惯例作「〜炭」。</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>来和我们一起跳吧！</t>
+          <t>Enako炭，来和我们一起跳吧！</t>
         </is>
       </c>
     </row>

--- a/歌词翻译/livedance_歌词对照_插白补充.xlsx
+++ b/歌词翻译/livedance_歌词对照_插白补充.xlsx
@@ -3143,17 +3143,17 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Enako炭，来和我们一起跳吧！</t>
+          <t>Enako酱来一起跳吧</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>同上。『Enako』为CoZ听写的呼喊（游戏文本查无此名，但音频确有喊名字）；用户拍板保留，-chan 按本补丁惯例作「〜炭」。</t>
+          <t>同上。『Enako』为CoZ听写的呼喊（游戏文本查无此名，但音频确有喊名字）；用户拍板保留并定稿措辞。</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Enako炭，来和我们一起跳吧！</t>
+          <t>Enako酱来一起跳吧</t>
         </is>
       </c>
     </row>
